--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0002T0006Z000C1N2_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0002T0006Z000C1N2_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.199269371447129</v>
+        <v>0.5198812728601585</v>
       </c>
       <c r="D2" t="n">
-        <v>87.62771407534315</v>
+        <v>14.23950353724326</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
